--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\clone\tcc-etec\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC8EE92-081B-4DE3-BC1C-082AC2C297D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ABD89D-70EE-4510-BB11-0DCE46B4CF49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -665,7 +665,7 @@
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -689,7 +689,7 @@
       </c>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="s">
         <v>12</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -770,7 +770,7 @@
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:12">
@@ -823,11 +823,13 @@
       <c r="D15" s="4">
         <v>4</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <v>10</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
         <f t="shared" ref="G15:G20" si="2">SUM(C15:F15)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -840,11 +842,13 @@
       <c r="D16" s="4">
         <v>10</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <v>8</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -855,11 +859,13 @@
         <v>0</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -870,11 +876,13 @@
       <c r="D18" s="4">
         <v>4</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4">
+        <v>5</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -887,7 +895,9 @@
       <c r="D19" s="4">
         <v>2</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
         <f t="shared" si="2"/>
@@ -902,13 +912,15 @@
         <v>1</v>
       </c>
       <c r="D20" s="7">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="E20" s="7">
+        <v>5</v>
+      </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\cu\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ABD89D-70EE-4510-BB11-0DCE46B4CF49}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35044621-C89E-4E22-8B7D-AD492D7D286A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -665,7 +665,7 @@
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -689,7 +689,7 @@
       </c>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
         <v>12</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -826,10 +826,12 @@
       <c r="E15" s="4">
         <v>10</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="4">
+        <v>2</v>
+      </c>
       <c r="G15" s="4">
         <f t="shared" ref="G15:G20" si="2">SUM(C15:F15)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -845,10 +847,12 @@
       <c r="E16" s="4">
         <v>8</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="4">
+        <v>8</v>
+      </c>
       <c r="G16" s="4">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -862,10 +866,12 @@
       <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4">
+        <v>4</v>
+      </c>
       <c r="G17" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -879,10 +885,12 @@
       <c r="E18" s="4">
         <v>5</v>
       </c>
-      <c r="F18" s="4"/>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
       <c r="G18" s="4">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -917,7 +925,9 @@
       <c r="E20" s="7">
         <v>5</v>
       </c>
-      <c r="F20" s="7"/>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
       <c r="G20" s="7">
         <f t="shared" si="2"/>
         <v>9</v>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\cu\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35044621-C89E-4E22-8B7D-AD492D7D286A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C835A-434B-4EBF-A6E3-EE575773BF0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -689,7 +689,7 @@
       </c>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" t="s">
         <v>12</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -827,11 +827,11 @@
         <v>10</v>
       </c>
       <c r="F15" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" ref="G15:G20" si="2">SUM(C15:F15)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -864,14 +864,14 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -886,11 +886,11 @@
         <v>5</v>
       </c>
       <c r="F18" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:11">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\Nova pasta (2)\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8C835A-434B-4EBF-A6E3-EE575773BF0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE79902A-8EDF-4DD4-8057-EE1ED78FEC66}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>35</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -718,7 +718,7 @@
       </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -982,13 +982,21 @@
       <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="C26" s="4">
+        <v>14</v>
+      </c>
+      <c r="D26" s="4">
+        <v>8</v>
+      </c>
+      <c r="E26" s="4">
+        <v>5</v>
+      </c>
+      <c r="F26" s="4">
+        <v>11</v>
+      </c>
       <c r="G26" s="4">
         <f t="shared" ref="G26:G31" si="3">SUM(C26:F26)</f>
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
@@ -1021,13 +1029,21 @@
       <c r="B29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="C29" s="4">
+        <v>4</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12</v>
+      </c>
+      <c r="E29" s="4">
+        <v>10</v>
+      </c>
+      <c r="F29" s="4">
+        <v>7</v>
+      </c>
       <c r="G29" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
